--- a/lab2/Работа LSFR.xlsx
+++ b/lab2/Работа LSFR.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\BSUIR\!sem4\IT\InformationTheory\lab2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CE0C890-15EE-4248-8E0D-FCE9CEF99EBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57C4E3E7-8AF2-4B50-BC68-7B5D2557CAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,14 +128,14 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Нейтральный" xfId="1" builtinId="28"/>
@@ -418,6 +418,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:AH63"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -427,144 +430,144 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
-      <c r="AE1" s="2"/>
-      <c r="AF1" s="2"/>
-      <c r="AG1" s="2"/>
-      <c r="AH1" s="3" t="s">
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
+      <c r="Q1" s="4"/>
+      <c r="R1" s="4"/>
+      <c r="S1" s="4"/>
+      <c r="T1" s="4"/>
+      <c r="U1" s="4"/>
+      <c r="V1" s="4"/>
+      <c r="W1" s="4"/>
+      <c r="X1" s="4"/>
+      <c r="Y1" s="4"/>
+      <c r="Z1" s="4"/>
+      <c r="AA1" s="4"/>
+      <c r="AB1" s="4"/>
+      <c r="AC1" s="4"/>
+      <c r="AD1" s="4"/>
+      <c r="AE1" s="4"/>
+      <c r="AF1" s="4"/>
+      <c r="AG1" s="4"/>
+      <c r="AH1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="C2" s="3">
+      <c r="C2" s="1">
         <v>31</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="1">
         <v>30</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="1">
         <v>29</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="1">
         <v>28</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="1">
         <v>27</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2" s="1">
         <v>26</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="1">
         <v>25</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="1">
         <v>24</v>
       </c>
-      <c r="K2" s="3">
+      <c r="K2" s="1">
         <v>23</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="1">
         <v>22</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="1">
         <v>21</v>
       </c>
-      <c r="N2" s="3">
+      <c r="N2" s="1">
         <v>20</v>
       </c>
-      <c r="O2" s="3">
+      <c r="O2" s="1">
         <v>19</v>
       </c>
-      <c r="P2" s="3">
+      <c r="P2" s="1">
         <v>18</v>
       </c>
-      <c r="Q2" s="3">
+      <c r="Q2" s="1">
         <v>17</v>
       </c>
-      <c r="R2" s="3">
+      <c r="R2" s="1">
         <v>16</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="1">
         <v>15</v>
       </c>
-      <c r="T2" s="3">
+      <c r="T2" s="1">
         <v>14</v>
       </c>
-      <c r="U2" s="3">
+      <c r="U2" s="1">
         <v>13</v>
       </c>
-      <c r="V2" s="3">
+      <c r="V2" s="1">
         <v>12</v>
       </c>
-      <c r="W2" s="3">
+      <c r="W2" s="1">
         <v>11</v>
       </c>
-      <c r="X2" s="3">
+      <c r="X2" s="1">
         <v>10</v>
       </c>
-      <c r="Y2" s="3">
+      <c r="Y2" s="1">
         <v>9</v>
       </c>
-      <c r="Z2" s="3">
+      <c r="Z2" s="1">
         <v>8</v>
       </c>
-      <c r="AA2" s="3">
+      <c r="AA2" s="1">
         <v>7</v>
       </c>
-      <c r="AB2" s="3">
+      <c r="AB2" s="1">
         <v>6</v>
       </c>
-      <c r="AC2" s="3">
+      <c r="AC2" s="1">
         <v>5</v>
       </c>
-      <c r="AD2" s="3">
+      <c r="AD2" s="1">
         <v>4</v>
       </c>
-      <c r="AE2" s="3">
+      <c r="AE2" s="1">
         <v>3</v>
       </c>
-      <c r="AF2" s="3">
+      <c r="AF2" s="1">
         <v>2</v>
       </c>
-      <c r="AG2" s="3">
-        <v>1</v>
-      </c>
-      <c r="AH2" s="4"/>
+      <c r="AG2" s="1">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="2"/>
     </row>
     <row r="3" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C3">
@@ -660,14 +663,14 @@
       <c r="AG3">
         <v>1</v>
       </c>
-      <c r="AH3" s="4">
+      <c r="AH3" s="2">
         <f>INT(_xlfn.XOR(C3,AE3))</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A4" s="1"/>
-      <c r="B4" s="3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="1">
         <v>1</v>
       </c>
       <c r="C4">
@@ -794,14 +797,14 @@
         <f>AH3</f>
         <v>0</v>
       </c>
-      <c r="AH4" s="4">
+      <c r="AH4" s="2">
         <f>INT(_xlfn.XOR(C4,AE4))</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A5" s="1"/>
-      <c r="B5" s="3">
+      <c r="A5" s="3"/>
+      <c r="B5" s="1">
         <v>2</v>
       </c>
       <c r="C5">
@@ -928,14 +931,14 @@
         <f t="shared" ref="AG5:AG63" si="1">AH4</f>
         <v>0</v>
       </c>
-      <c r="AH5" s="4">
+      <c r="AH5" s="2">
         <f t="shared" ref="AH5:AH63" si="2">INT(_xlfn.XOR(C5,AE5))</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A6" s="1"/>
-      <c r="B6" s="3">
+      <c r="A6" s="3"/>
+      <c r="B6" s="1">
         <v>3</v>
       </c>
       <c r="C6">
@@ -1062,14 +1065,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH6" s="4">
+      <c r="AH6" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A7" s="1"/>
-      <c r="B7" s="3">
+      <c r="A7" s="3"/>
+      <c r="B7" s="1">
         <v>4</v>
       </c>
       <c r="C7">
@@ -1196,14 +1199,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH7" s="4">
+      <c r="AH7" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A8" s="1"/>
-      <c r="B8" s="3">
+      <c r="A8" s="3"/>
+      <c r="B8" s="1">
         <v>5</v>
       </c>
       <c r="C8">
@@ -1330,14 +1333,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH8" s="4">
+      <c r="AH8" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="3">
+      <c r="A9" s="3"/>
+      <c r="B9" s="1">
         <v>6</v>
       </c>
       <c r="C9">
@@ -1464,14 +1467,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH9" s="4">
+      <c r="AH9" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="3">
+      <c r="A10" s="3"/>
+      <c r="B10" s="1">
         <v>7</v>
       </c>
       <c r="C10">
@@ -1598,14 +1601,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH10" s="4">
+      <c r="AH10" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A11" s="1"/>
-      <c r="B11" s="3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="1">
         <v>8</v>
       </c>
       <c r="C11">
@@ -1732,14 +1735,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH11" s="4">
+      <c r="AH11" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A12" s="1"/>
-      <c r="B12" s="3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="1">
         <v>9</v>
       </c>
       <c r="C12">
@@ -1866,14 +1869,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH12" s="4">
+      <c r="AH12" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A13" s="1"/>
-      <c r="B13" s="3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="1">
         <v>10</v>
       </c>
       <c r="C13">
@@ -2000,14 +2003,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH13" s="4">
+      <c r="AH13" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A14" s="1"/>
-      <c r="B14" s="3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="1">
         <v>11</v>
       </c>
       <c r="C14">
@@ -2134,14 +2137,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH14" s="4">
+      <c r="AH14" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A15" s="1"/>
-      <c r="B15" s="3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="1">
         <v>12</v>
       </c>
       <c r="C15">
@@ -2268,14 +2271,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH15" s="4">
+      <c r="AH15" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A16" s="1"/>
-      <c r="B16" s="3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="1">
         <v>13</v>
       </c>
       <c r="C16">
@@ -2402,14 +2405,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH16" s="4">
+      <c r="AH16" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A17" s="1"/>
-      <c r="B17" s="3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="1">
         <v>14</v>
       </c>
       <c r="C17">
@@ -2536,14 +2539,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH17" s="4">
+      <c r="AH17" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A18" s="1"/>
-      <c r="B18" s="3">
+      <c r="A18" s="3"/>
+      <c r="B18" s="1">
         <v>15</v>
       </c>
       <c r="C18">
@@ -2670,14 +2673,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH18" s="4">
+      <c r="AH18" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A19" s="1"/>
-      <c r="B19" s="3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="1">
         <v>16</v>
       </c>
       <c r="C19">
@@ -2804,14 +2807,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH19" s="4">
+      <c r="AH19" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="3">
+      <c r="A20" s="3"/>
+      <c r="B20" s="1">
         <v>17</v>
       </c>
       <c r="C20">
@@ -2938,14 +2941,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH20" s="4">
+      <c r="AH20" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A21" s="1"/>
-      <c r="B21" s="3">
+      <c r="A21" s="3"/>
+      <c r="B21" s="1">
         <v>18</v>
       </c>
       <c r="C21">
@@ -3072,14 +3075,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH21" s="4">
+      <c r="AH21" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A22" s="1"/>
-      <c r="B22" s="3">
+      <c r="A22" s="3"/>
+      <c r="B22" s="1">
         <v>19</v>
       </c>
       <c r="C22">
@@ -3206,14 +3209,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH22" s="4">
+      <c r="AH22" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A23" s="1"/>
-      <c r="B23" s="3">
+      <c r="A23" s="3"/>
+      <c r="B23" s="1">
         <v>20</v>
       </c>
       <c r="C23">
@@ -3340,14 +3343,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH23" s="4">
+      <c r="AH23" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A24" s="1"/>
-      <c r="B24" s="3">
+      <c r="A24" s="3"/>
+      <c r="B24" s="1">
         <v>21</v>
       </c>
       <c r="C24">
@@ -3474,14 +3477,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH24" s="4">
+      <c r="AH24" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A25" s="1"/>
-      <c r="B25" s="3">
+      <c r="A25" s="3"/>
+      <c r="B25" s="1">
         <v>22</v>
       </c>
       <c r="C25">
@@ -3608,14 +3611,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH25" s="4">
+      <c r="AH25" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A26" s="1"/>
-      <c r="B26" s="3">
+      <c r="A26" s="3"/>
+      <c r="B26" s="1">
         <v>23</v>
       </c>
       <c r="C26">
@@ -3742,14 +3745,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH26" s="4">
+      <c r="AH26" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A27" s="1"/>
-      <c r="B27" s="3">
+      <c r="A27" s="3"/>
+      <c r="B27" s="1">
         <v>24</v>
       </c>
       <c r="C27">
@@ -3876,14 +3879,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH27" s="4">
+      <c r="AH27" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A28" s="1"/>
-      <c r="B28" s="3">
+      <c r="A28" s="3"/>
+      <c r="B28" s="1">
         <v>25</v>
       </c>
       <c r="C28">
@@ -4010,14 +4013,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH28" s="4">
+      <c r="AH28" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A29" s="1"/>
-      <c r="B29" s="3">
+      <c r="A29" s="3"/>
+      <c r="B29" s="1">
         <v>26</v>
       </c>
       <c r="C29">
@@ -4144,14 +4147,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH29" s="4">
+      <c r="AH29" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A30" s="1"/>
-      <c r="B30" s="3">
+      <c r="A30" s="3"/>
+      <c r="B30" s="1">
         <v>27</v>
       </c>
       <c r="C30">
@@ -4278,14 +4281,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH30" s="4">
+      <c r="AH30" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A31" s="1"/>
-      <c r="B31" s="3">
+      <c r="A31" s="3"/>
+      <c r="B31" s="1">
         <v>28</v>
       </c>
       <c r="C31">
@@ -4412,14 +4415,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH31" s="4">
+      <c r="AH31" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A32" s="1"/>
-      <c r="B32" s="3">
+      <c r="A32" s="3"/>
+      <c r="B32" s="1">
         <v>29</v>
       </c>
       <c r="C32">
@@ -4546,14 +4549,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH32" s="4">
+      <c r="AH32" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A33" s="1"/>
-      <c r="B33" s="3">
+      <c r="A33" s="3"/>
+      <c r="B33" s="1">
         <v>30</v>
       </c>
       <c r="C33">
@@ -4680,14 +4683,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH33" s="4">
+      <c r="AH33" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A34" s="1"/>
-      <c r="B34" s="3">
+      <c r="A34" s="3"/>
+      <c r="B34" s="1">
         <v>31</v>
       </c>
       <c r="C34">
@@ -4814,14 +4817,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH34" s="4">
+      <c r="AH34" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A35" s="1"/>
-      <c r="B35" s="3">
+      <c r="A35" s="3"/>
+      <c r="B35" s="1">
         <v>32</v>
       </c>
       <c r="C35">
@@ -4948,14 +4951,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH35" s="4">
+      <c r="AH35" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A36" s="1"/>
-      <c r="B36" s="3">
+      <c r="A36" s="3"/>
+      <c r="B36" s="1">
         <v>33</v>
       </c>
       <c r="C36">
@@ -5082,14 +5085,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH36" s="4">
+      <c r="AH36" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A37" s="1"/>
-      <c r="B37" s="3">
+      <c r="A37" s="3"/>
+      <c r="B37" s="1">
         <v>34</v>
       </c>
       <c r="C37">
@@ -5216,14 +5219,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH37" s="4">
+      <c r="AH37" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A38" s="1"/>
-      <c r="B38" s="3">
+      <c r="A38" s="3"/>
+      <c r="B38" s="1">
         <v>35</v>
       </c>
       <c r="C38">
@@ -5350,14 +5353,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH38" s="4">
+      <c r="AH38" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A39" s="1"/>
-      <c r="B39" s="3">
+      <c r="A39" s="3"/>
+      <c r="B39" s="1">
         <v>36</v>
       </c>
       <c r="C39">
@@ -5484,14 +5487,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH39" s="4">
+      <c r="AH39" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A40" s="1"/>
-      <c r="B40" s="3">
+      <c r="A40" s="3"/>
+      <c r="B40" s="1">
         <v>37</v>
       </c>
       <c r="C40">
@@ -5618,14 +5621,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH40" s="4">
+      <c r="AH40" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A41" s="1"/>
-      <c r="B41" s="3">
+      <c r="A41" s="3"/>
+      <c r="B41" s="1">
         <v>38</v>
       </c>
       <c r="C41">
@@ -5752,14 +5755,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH41" s="4">
+      <c r="AH41" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A42" s="1"/>
-      <c r="B42" s="3">
+      <c r="A42" s="3"/>
+      <c r="B42" s="1">
         <v>39</v>
       </c>
       <c r="C42">
@@ -5886,14 +5889,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH42" s="4">
+      <c r="AH42" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A43" s="1"/>
-      <c r="B43" s="3">
+      <c r="A43" s="3"/>
+      <c r="B43" s="1">
         <v>40</v>
       </c>
       <c r="C43">
@@ -6020,14 +6023,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH43" s="4">
+      <c r="AH43" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A44" s="1"/>
-      <c r="B44" s="3">
+      <c r="A44" s="3"/>
+      <c r="B44" s="1">
         <v>41</v>
       </c>
       <c r="C44">
@@ -6154,14 +6157,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH44" s="4">
+      <c r="AH44" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A45" s="1"/>
-      <c r="B45" s="3">
+      <c r="A45" s="3"/>
+      <c r="B45" s="1">
         <v>42</v>
       </c>
       <c r="C45">
@@ -6288,14 +6291,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH45" s="4">
+      <c r="AH45" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A46" s="1"/>
-      <c r="B46" s="3">
+      <c r="A46" s="3"/>
+      <c r="B46" s="1">
         <v>43</v>
       </c>
       <c r="C46">
@@ -6422,14 +6425,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH46" s="4">
+      <c r="AH46" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A47" s="1"/>
-      <c r="B47" s="3">
+      <c r="A47" s="3"/>
+      <c r="B47" s="1">
         <v>44</v>
       </c>
       <c r="C47">
@@ -6556,14 +6559,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH47" s="4">
+      <c r="AH47" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A48" s="1"/>
-      <c r="B48" s="3">
+      <c r="A48" s="3"/>
+      <c r="B48" s="1">
         <v>45</v>
       </c>
       <c r="C48">
@@ -6690,14 +6693,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH48" s="4">
+      <c r="AH48" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A49" s="1"/>
-      <c r="B49" s="3">
+      <c r="A49" s="3"/>
+      <c r="B49" s="1">
         <v>46</v>
       </c>
       <c r="C49">
@@ -6824,14 +6827,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH49" s="4">
+      <c r="AH49" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A50" s="1"/>
-      <c r="B50" s="3">
+      <c r="A50" s="3"/>
+      <c r="B50" s="1">
         <v>47</v>
       </c>
       <c r="C50">
@@ -6958,14 +6961,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH50" s="4">
+      <c r="AH50" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A51" s="1"/>
-      <c r="B51" s="3">
+      <c r="A51" s="3"/>
+      <c r="B51" s="1">
         <v>48</v>
       </c>
       <c r="C51">
@@ -7092,14 +7095,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH51" s="4">
+      <c r="AH51" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A52" s="1"/>
-      <c r="B52" s="3">
+      <c r="A52" s="3"/>
+      <c r="B52" s="1">
         <v>49</v>
       </c>
       <c r="C52">
@@ -7226,14 +7229,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH52" s="4">
+      <c r="AH52" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A53" s="1"/>
-      <c r="B53" s="3">
+      <c r="A53" s="3"/>
+      <c r="B53" s="1">
         <v>50</v>
       </c>
       <c r="C53">
@@ -7360,14 +7363,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH53" s="4">
+      <c r="AH53" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A54" s="1"/>
-      <c r="B54" s="3">
+      <c r="A54" s="3"/>
+      <c r="B54" s="1">
         <v>51</v>
       </c>
       <c r="C54">
@@ -7494,14 +7497,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH54" s="4">
+      <c r="AH54" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A55" s="1"/>
-      <c r="B55" s="3">
+      <c r="A55" s="3"/>
+      <c r="B55" s="1">
         <v>52</v>
       </c>
       <c r="C55">
@@ -7628,14 +7631,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH55" s="4">
+      <c r="AH55" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A56" s="1"/>
-      <c r="B56" s="3">
+      <c r="A56" s="3"/>
+      <c r="B56" s="1">
         <v>53</v>
       </c>
       <c r="C56">
@@ -7762,14 +7765,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH56" s="4">
+      <c r="AH56" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A57" s="1"/>
-      <c r="B57" s="3">
+      <c r="A57" s="3"/>
+      <c r="B57" s="1">
         <v>54</v>
       </c>
       <c r="C57">
@@ -7896,14 +7899,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH57" s="4">
+      <c r="AH57" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A58" s="1"/>
-      <c r="B58" s="3">
+      <c r="A58" s="3"/>
+      <c r="B58" s="1">
         <v>55</v>
       </c>
       <c r="C58">
@@ -8030,14 +8033,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH58" s="4">
+      <c r="AH58" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A59" s="1"/>
-      <c r="B59" s="3">
+      <c r="A59" s="3"/>
+      <c r="B59" s="1">
         <v>56</v>
       </c>
       <c r="C59">
@@ -8164,14 +8167,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH59" s="4">
+      <c r="AH59" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A60" s="1"/>
-      <c r="B60" s="3">
+      <c r="A60" s="3"/>
+      <c r="B60" s="1">
         <v>57</v>
       </c>
       <c r="C60">
@@ -8298,14 +8301,14 @@
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="AH60" s="4">
+      <c r="AH60" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A61" s="1"/>
-      <c r="B61" s="3">
+      <c r="A61" s="3"/>
+      <c r="B61" s="1">
         <v>58</v>
       </c>
       <c r="C61">
@@ -8432,14 +8435,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH61" s="4">
+      <c r="AH61" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A62" s="1"/>
-      <c r="B62" s="3">
+      <c r="A62" s="3"/>
+      <c r="B62" s="1">
         <v>59</v>
       </c>
       <c r="C62">
@@ -8566,14 +8569,14 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH62" s="4">
+      <c r="AH62" s="2">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A63" s="1"/>
-      <c r="B63" s="3">
+      <c r="A63" s="3"/>
+      <c r="B63" s="1">
         <v>60</v>
       </c>
       <c r="C63">
@@ -8700,7 +8703,7 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="AH63" s="4">
+      <c r="AH63" s="2">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
@@ -8711,5 +8714,6 @@
     <mergeCell ref="C1:AG1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="40" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>